--- a/data/trans_bre/P14B23-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Clase-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,66</t>
+          <t>-1,21; 3,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,55</t>
+          <t>0,14; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,26</t>
+          <t>0,78; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-85,14; 706,62</t>
+          <t>-71,13; 664,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 1420,57</t>
+          <t>-25,62; 1229,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 418,05</t>
+          <t>10,95; 441,65</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,86</t>
+          <t>-1,14; 3,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,26</t>
+          <t>-0,8; 3,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,04</t>
+          <t>1,87; 6,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 386,51</t>
+          <t>-48,64; 368,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 677,32</t>
+          <t>-50,81; 530,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,38; 443,1</t>
+          <t>43,1; 420,1</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,37</t>
+          <t>0,66; 8,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,13</t>
+          <t>3,73; 13,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,54</t>
+          <t>2,75; 11,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 268,17</t>
+          <t>9,75; 277,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>156,95; 1625,72</t>
+          <t>163,62; 1856,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,51; 919,69</t>
+          <t>50,22; 827,48</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,45</t>
+          <t>2,05; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,47</t>
+          <t>0,44; 4,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,89</t>
+          <t>-1,66; 3,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,89; 284,53</t>
+          <t>51,72; 270,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 248,59</t>
+          <t>12,49; 209,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 100,68</t>
+          <t>-30,13; 104,37</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,09</t>
+          <t>7,26; 12,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,29</t>
+          <t>3,67; 9,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,85</t>
+          <t>1,2; 6,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255,58; 1318,42</t>
+          <t>256,36; 1379,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,49; 422,62</t>
+          <t>78,96; 405,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 205,61</t>
+          <t>17,6; 207,89</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,75</t>
+          <t>7,96; 11,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,08</t>
+          <t>6,22; 9,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,7</t>
+          <t>-1,62; 6,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 307,3</t>
+          <t>-20,81; 320,39</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,7</t>
+          <t>4,52; 6,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,81</t>
+          <t>3,78; 5,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,97</t>
+          <t>2,11; 4,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151,79; 324,63</t>
+          <t>154,93; 330,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>162,78; 359,15</t>
+          <t>159,73; 344,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,32; 166,41</t>
+          <t>53,99; 171,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P14B23-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>149,64%</t>
+          <t>167,73%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,57</t>
+          <t>-1,15; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,47</t>
+          <t>0,22; 4,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,31</t>
+          <t>1,1; 5,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 664,08</t>
+          <t>-70,91; 663,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 1229,54</t>
+          <t>-9,13; 1246,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 441,65</t>
+          <t>21,27; 446,73</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>168,07%</t>
+          <t>178,99%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,8</t>
+          <t>-1,29; 3,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,27</t>
+          <t>-0,73; 3,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,81</t>
+          <t>2,12; 7,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 368,44</t>
+          <t>-48,1; 370,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 530,3</t>
+          <t>-49,32; 521,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,1; 420,1</t>
+          <t>53,08; 498,95</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>199,78%</t>
+          <t>108,35%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,77</t>
+          <t>0,74; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 13,35</t>
+          <t>3,71; 14,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,8</t>
+          <t>1,5; 9,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 277,44</t>
+          <t>12,86; 266,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>163,62; 1856,12</t>
+          <t>167,76; 1916,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,22; 827,48</t>
+          <t>19,71; 291,56</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,19</t>
+          <t>2,0; 6,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,19</t>
+          <t>0,61; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,95</t>
+          <t>1,29; 5,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,72; 270,48</t>
+          <t>53,72; 274,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 209,73</t>
+          <t>14,64; 220,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 104,37</t>
+          <t>22,33; 150,47</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>136,73%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,22</t>
+          <t>7,08; 12,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,15</t>
+          <t>4,0; 9,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,93</t>
+          <t>3,56; 8,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256,36; 1379,12</t>
+          <t>252,86; 1460,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,96; 405,66</t>
+          <t>89,06; 410,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 207,89</t>
+          <t>59,23; 272,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,67</t>
+          <t>8,12; 11,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,86</t>
+          <t>6,22; 9,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,76</t>
+          <t>-1,85; 6,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 320,39</t>
+          <t>-27,7; 296,57</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>101,01%</t>
+          <t>110,2%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,62</t>
+          <t>4,67; 6,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,77</t>
+          <t>3,78; 5,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,99</t>
+          <t>3,19; 5,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154,93; 330,29</t>
+          <t>163,48; 344,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>159,73; 344,65</t>
+          <t>162,12; 361,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,99; 171,46</t>
+          <t>71,11; 157,42</t>
         </is>
       </c>
     </row>
